--- a/Result/profitability/5347.xlsx
+++ b/Result/profitability/5347.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.45</v>
       </c>
       <c r="M2" t="n">
-        <v>1.04625</v>
+        <v>1.08625</v>
       </c>
       <c r="N2" t="n">
-        <v>28.47125</v>
+        <v>28.8825</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.28</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9187500000000001</v>
+        <v>0.9837500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>27.2125</v>
+        <v>27.6675</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.19</v>
       </c>
       <c r="M4" t="n">
-        <v>0.805</v>
+        <v>0.84375</v>
       </c>
       <c r="N4" t="n">
-        <v>25.6775</v>
+        <v>25.955</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.31</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6025</v>
+        <v>0.6662500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>20.71875</v>
+        <v>21.25375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0.40125</v>
+        <v>0.4875</v>
       </c>
       <c r="N6" t="n">
-        <v>13.15125</v>
+        <v>13.83875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.09</v>
       </c>
       <c r="M7" t="n">
-        <v>0.29625</v>
+        <v>0.3800000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>11.53875</v>
+        <v>12.14</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.41</v>
       </c>
       <c r="M8" t="n">
-        <v>0.22875</v>
+        <v>0.2787500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>10.87125</v>
+        <v>11.25</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>0.08250000000000002</v>
       </c>
       <c r="N9" t="n">
-        <v>8.6175</v>
+        <v>8.617500000000001</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>0.04250000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>7.0625</v>
+        <v>7.062500000000001</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>0.05000000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>7.4175</v>
+        <v>7.417500000000001</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>0.09000000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>8.895</v>
+        <v>8.895000000000001</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>14245</v>
+      </c>
+      <c r="D75" t="n">
+        <v>9640</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4604</v>
+      </c>
+      <c r="F75" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2901</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>20.37%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>412</v>
+      </c>
+      <c r="J75" t="n">
+        <v>3313</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2975</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.1925</v>
+      </c>
+      <c r="N75" t="n">
+        <v>28.97375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.4000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3278688524590165</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.030000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.103448275862069</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.4594594594594594</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.280000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.152639087018545</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
